--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_12-08-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_12-08-2025.xlsx
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f66b55+79621]
-	GetHandleVerifier [0x0x7ff754f66bb0+79712]
-	(No symbol) [0x0x7ff754cfc0ea]
-	(No symbol) [0x0x7ff754d52f56]
-	(No symbol) [0x0x7ff754d5320c]
-	(No symbol) [0x0x7ff754da65b7]
-	(No symbol) [0x0x7ff754d7b17f]
-	(No symbol) [0x0x7ff754da33d0]
-	(No symbol) [0x0x7ff754d7af13]
-	(No symbol) [0x0x7ff754d44151]
-	(No symbol) [0x0x7ff754d44ee3]
-	GetHandleVerifier [0x0x7ff75522686d+2962461]
-	GetHandleVerifier [0x0x7ff755220b8d+2938685]
-	GetHandleVerifier [0x0x7ff75523f74d+3064573]
-	GetHandleVerifier [0x0x7ff754f80c9e+186446]
-	GetHandleVerifier [0x0x7ff754f88a6f+218655]
-	GetHandleVerifier [0x0x7ff754f6f944+115956]
-	GetHandleVerifier [0x0x7ff754f6faf9+116393]
-	GetHandleVerifier [0x0x7ff754f55f28+10968]
+	GetHandleVerifier [0x0x7ff733fa6b55+79621]
+	GetHandleVerifier [0x0x7ff733fa6bb0+79712]
+	(No symbol) [0x0x7ff733d3c0ea]
+	(No symbol) [0x0x7ff733d92f56]
+	(No symbol) [0x0x7ff733d9320c]
+	(No symbol) [0x0x7ff733de65b7]
+	(No symbol) [0x0x7ff733dbb17f]
+	(No symbol) [0x0x7ff733de33d0]
+	(No symbol) [0x0x7ff733dbaf13]
+	(No symbol) [0x0x7ff733d84151]
+	(No symbol) [0x0x7ff733d84ee3]
+	GetHandleVerifier [0x0x7ff73426686d+2962461]
+	GetHandleVerifier [0x0x7ff734260b8d+2938685]
+	GetHandleVerifier [0x0x7ff73427f74d+3064573]
+	GetHandleVerifier [0x0x7ff733fc0c9e+186446]
+	GetHandleVerifier [0x0x7ff733fc8a6f+218655]
+	GetHandleVerifier [0x0x7ff733faf944+115956]
+	GetHandleVerifier [0x0x7ff733fafaf9+116393]
+	GetHandleVerifier [0x0x7ff733f95f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f66b55+79621]
-	GetHandleVerifier [0x0x7ff754f66bb0+79712]
-	(No symbol) [0x0x7ff754cfc0ea]
-	(No symbol) [0x0x7ff754d52f56]
-	(No symbol) [0x0x7ff754d5320c]
-	(No symbol) [0x0x7ff754da65b7]
-	(No symbol) [0x0x7ff754d7b17f]
-	(No symbol) [0x0x7ff754da33d0]
-	(No symbol) [0x0x7ff754d7af13]
-	(No symbol) [0x0x7ff754d44151]
-	(No symbol) [0x0x7ff754d44ee3]
-	GetHandleVerifier [0x0x7ff75522686d+2962461]
-	GetHandleVerifier [0x0x7ff755220b8d+2938685]
-	GetHandleVerifier [0x0x7ff75523f74d+3064573]
-	GetHandleVerifier [0x0x7ff754f80c9e+186446]
-	GetHandleVerifier [0x0x7ff754f88a6f+218655]
-	GetHandleVerifier [0x0x7ff754f6f944+115956]
-	GetHandleVerifier [0x0x7ff754f6faf9+116393]
-	GetHandleVerifier [0x0x7ff754f55f28+10968]
+	GetHandleVerifier [0x0x7ff733fa6b55+79621]
+	GetHandleVerifier [0x0x7ff733fa6bb0+79712]
+	(No symbol) [0x0x7ff733d3c0ea]
+	(No symbol) [0x0x7ff733d92f56]
+	(No symbol) [0x0x7ff733d9320c]
+	(No symbol) [0x0x7ff733de65b7]
+	(No symbol) [0x0x7ff733dbb17f]
+	(No symbol) [0x0x7ff733de33d0]
+	(No symbol) [0x0x7ff733dbaf13]
+	(No symbol) [0x0x7ff733d84151]
+	(No symbol) [0x0x7ff733d84ee3]
+	GetHandleVerifier [0x0x7ff73426686d+2962461]
+	GetHandleVerifier [0x0x7ff734260b8d+2938685]
+	GetHandleVerifier [0x0x7ff73427f74d+3064573]
+	GetHandleVerifier [0x0x7ff733fc0c9e+186446]
+	GetHandleVerifier [0x0x7ff733fc8a6f+218655]
+	GetHandleVerifier [0x0x7ff733faf944+115956]
+	GetHandleVerifier [0x0x7ff733fafaf9+116393]
+	GetHandleVerifier [0x0x7ff733f95f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f66b55+79621]
-	GetHandleVerifier [0x0x7ff754f66bb0+79712]
-	(No symbol) [0x0x7ff754cfc0ea]
-	(No symbol) [0x0x7ff754d52f56]
-	(No symbol) [0x0x7ff754d5320c]
-	(No symbol) [0x0x7ff754da65b7]
-	(No symbol) [0x0x7ff754d7b17f]
-	(No symbol) [0x0x7ff754da33d0]
-	(No symbol) [0x0x7ff754d7af13]
-	(No symbol) [0x0x7ff754d44151]
-	(No symbol) [0x0x7ff754d44ee3]
-	GetHandleVerifier [0x0x7ff75522686d+2962461]
-	GetHandleVerifier [0x0x7ff755220b8d+2938685]
-	GetHandleVerifier [0x0x7ff75523f74d+3064573]
-	GetHandleVerifier [0x0x7ff754f80c9e+186446]
-	GetHandleVerifier [0x0x7ff754f88a6f+218655]
-	GetHandleVerifier [0x0x7ff754f6f944+115956]
-	GetHandleVerifier [0x0x7ff754f6faf9+116393]
-	GetHandleVerifier [0x0x7ff754f55f28+10968]
+	GetHandleVerifier [0x0x7ff733fa6b55+79621]
+	GetHandleVerifier [0x0x7ff733fa6bb0+79712]
+	(No symbol) [0x0x7ff733d3c0ea]
+	(No symbol) [0x0x7ff733d92f56]
+	(No symbol) [0x0x7ff733d9320c]
+	(No symbol) [0x0x7ff733de65b7]
+	(No symbol) [0x0x7ff733dbb17f]
+	(No symbol) [0x0x7ff733de33d0]
+	(No symbol) [0x0x7ff733dbaf13]
+	(No symbol) [0x0x7ff733d84151]
+	(No symbol) [0x0x7ff733d84ee3]
+	GetHandleVerifier [0x0x7ff73426686d+2962461]
+	GetHandleVerifier [0x0x7ff734260b8d+2938685]
+	GetHandleVerifier [0x0x7ff73427f74d+3064573]
+	GetHandleVerifier [0x0x7ff733fc0c9e+186446]
+	GetHandleVerifier [0x0x7ff733fc8a6f+218655]
+	GetHandleVerifier [0x0x7ff733faf944+115956]
+	GetHandleVerifier [0x0x7ff733fafaf9+116393]
+	GetHandleVerifier [0x0x7ff733f95f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -916,7 +916,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>£16.65</t>
+          <t>£16.50</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f66b55+79621]
-	GetHandleVerifier [0x0x7ff754f66bb0+79712]
-	(No symbol) [0x0x7ff754cfc0ea]
-	(No symbol) [0x0x7ff754d52f56]
-	(No symbol) [0x0x7ff754d5320c]
-	(No symbol) [0x0x7ff754da65b7]
-	(No symbol) [0x0x7ff754d7b17f]
-	(No symbol) [0x0x7ff754da33d0]
-	(No symbol) [0x0x7ff754d7af13]
-	(No symbol) [0x0x7ff754d44151]
-	(No symbol) [0x0x7ff754d44ee3]
-	GetHandleVerifier [0x0x7ff75522686d+2962461]
-	GetHandleVerifier [0x0x7ff755220b8d+2938685]
-	GetHandleVerifier [0x0x7ff75523f74d+3064573]
-	GetHandleVerifier [0x0x7ff754f80c9e+186446]
-	GetHandleVerifier [0x0x7ff754f88a6f+218655]
-	GetHandleVerifier [0x0x7ff754f6f944+115956]
-	GetHandleVerifier [0x0x7ff754f6faf9+116393]
-	GetHandleVerifier [0x0x7ff754f55f28+10968]
+	GetHandleVerifier [0x0x7ff733fa6b55+79621]
+	GetHandleVerifier [0x0x7ff733fa6bb0+79712]
+	(No symbol) [0x0x7ff733d3c0ea]
+	(No symbol) [0x0x7ff733d92f56]
+	(No symbol) [0x0x7ff733d9320c]
+	(No symbol) [0x0x7ff733de65b7]
+	(No symbol) [0x0x7ff733dbb17f]
+	(No symbol) [0x0x7ff733de33d0]
+	(No symbol) [0x0x7ff733dbaf13]
+	(No symbol) [0x0x7ff733d84151]
+	(No symbol) [0x0x7ff733d84ee3]
+	GetHandleVerifier [0x0x7ff73426686d+2962461]
+	GetHandleVerifier [0x0x7ff734260b8d+2938685]
+	GetHandleVerifier [0x0x7ff73427f74d+3064573]
+	GetHandleVerifier [0x0x7ff733fc0c9e+186446]
+	GetHandleVerifier [0x0x7ff733fc8a6f+218655]
+	GetHandleVerifier [0x0x7ff733faf944+115956]
+	GetHandleVerifier [0x0x7ff733fafaf9+116393]
+	GetHandleVerifier [0x0x7ff733f95f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f66b55+79621]
-	GetHandleVerifier [0x0x7ff754f66bb0+79712]
-	(No symbol) [0x0x7ff754cfc0ea]
-	(No symbol) [0x0x7ff754d52f56]
-	(No symbol) [0x0x7ff754d5320c]
-	(No symbol) [0x0x7ff754da65b7]
-	(No symbol) [0x0x7ff754d7b17f]
-	(No symbol) [0x0x7ff754da33d0]
-	(No symbol) [0x0x7ff754d7af13]
-	(No symbol) [0x0x7ff754d44151]
-	(No symbol) [0x0x7ff754d44ee3]
-	GetHandleVerifier [0x0x7ff75522686d+2962461]
-	GetHandleVerifier [0x0x7ff755220b8d+2938685]
-	GetHandleVerifier [0x0x7ff75523f74d+3064573]
-	GetHandleVerifier [0x0x7ff754f80c9e+186446]
-	GetHandleVerifier [0x0x7ff754f88a6f+218655]
-	GetHandleVerifier [0x0x7ff754f6f944+115956]
-	GetHandleVerifier [0x0x7ff754f6faf9+116393]
-	GetHandleVerifier [0x0x7ff754f55f28+10968]
+	GetHandleVerifier [0x0x7ff733fa6b55+79621]
+	GetHandleVerifier [0x0x7ff733fa6bb0+79712]
+	(No symbol) [0x0x7ff733d3c0ea]
+	(No symbol) [0x0x7ff733d92f56]
+	(No symbol) [0x0x7ff733d9320c]
+	(No symbol) [0x0x7ff733de65b7]
+	(No symbol) [0x0x7ff733dbb17f]
+	(No symbol) [0x0x7ff733de33d0]
+	(No symbol) [0x0x7ff733dbaf13]
+	(No symbol) [0x0x7ff733d84151]
+	(No symbol) [0x0x7ff733d84ee3]
+	GetHandleVerifier [0x0x7ff73426686d+2962461]
+	GetHandleVerifier [0x0x7ff734260b8d+2938685]
+	GetHandleVerifier [0x0x7ff73427f74d+3064573]
+	GetHandleVerifier [0x0x7ff733fc0c9e+186446]
+	GetHandleVerifier [0x0x7ff733fc8a6f+218655]
+	GetHandleVerifier [0x0x7ff733faf944+115956]
+	GetHandleVerifier [0x0x7ff733fafaf9+116393]
+	GetHandleVerifier [0x0x7ff733f95f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f66b55+79621]
-	GetHandleVerifier [0x0x7ff754f66bb0+79712]
-	(No symbol) [0x0x7ff754cfc0ea]
-	(No symbol) [0x0x7ff754d52f56]
-	(No symbol) [0x0x7ff754d5320c]
-	(No symbol) [0x0x7ff754da65b7]
-	(No symbol) [0x0x7ff754d7b17f]
-	(No symbol) [0x0x7ff754da33d0]
-	(No symbol) [0x0x7ff754d7af13]
-	(No symbol) [0x0x7ff754d44151]
-	(No symbol) [0x0x7ff754d44ee3]
-	GetHandleVerifier [0x0x7ff75522686d+2962461]
-	GetHandleVerifier [0x0x7ff755220b8d+2938685]
-	GetHandleVerifier [0x0x7ff75523f74d+3064573]
-	GetHandleVerifier [0x0x7ff754f80c9e+186446]
-	GetHandleVerifier [0x0x7ff754f88a6f+218655]
-	GetHandleVerifier [0x0x7ff754f6f944+115956]
-	GetHandleVerifier [0x0x7ff754f6faf9+116393]
-	GetHandleVerifier [0x0x7ff754f55f28+10968]
+	GetHandleVerifier [0x0x7ff733fa6b55+79621]
+	GetHandleVerifier [0x0x7ff733fa6bb0+79712]
+	(No symbol) [0x0x7ff733d3c0ea]
+	(No symbol) [0x0x7ff733d92f56]
+	(No symbol) [0x0x7ff733d9320c]
+	(No symbol) [0x0x7ff733de65b7]
+	(No symbol) [0x0x7ff733dbb17f]
+	(No symbol) [0x0x7ff733de33d0]
+	(No symbol) [0x0x7ff733dbaf13]
+	(No symbol) [0x0x7ff733d84151]
+	(No symbol) [0x0x7ff733d84ee3]
+	GetHandleVerifier [0x0x7ff73426686d+2962461]
+	GetHandleVerifier [0x0x7ff734260b8d+2938685]
+	GetHandleVerifier [0x0x7ff73427f74d+3064573]
+	GetHandleVerifier [0x0x7ff733fc0c9e+186446]
+	GetHandleVerifier [0x0x7ff733fc8a6f+218655]
+	GetHandleVerifier [0x0x7ff733faf944+115956]
+	GetHandleVerifier [0x0x7ff733fafaf9+116393]
+	GetHandleVerifier [0x0x7ff733f95f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f66b55+79621]
-	GetHandleVerifier [0x0x7ff754f66bb0+79712]
-	(No symbol) [0x0x7ff754cfc0ea]
-	(No symbol) [0x0x7ff754d52f56]
-	(No symbol) [0x0x7ff754d5320c]
-	(No symbol) [0x0x7ff754da65b7]
-	(No symbol) [0x0x7ff754d7b17f]
-	(No symbol) [0x0x7ff754da33d0]
-	(No symbol) [0x0x7ff754d7af13]
-	(No symbol) [0x0x7ff754d44151]
-	(No symbol) [0x0x7ff754d44ee3]
-	GetHandleVerifier [0x0x7ff75522686d+2962461]
-	GetHandleVerifier [0x0x7ff755220b8d+2938685]
-	GetHandleVerifier [0x0x7ff75523f74d+3064573]
-	GetHandleVerifier [0x0x7ff754f80c9e+186446]
-	GetHandleVerifier [0x0x7ff754f88a6f+218655]
-	GetHandleVerifier [0x0x7ff754f6f944+115956]
-	GetHandleVerifier [0x0x7ff754f6faf9+116393]
-	GetHandleVerifier [0x0x7ff754f55f28+10968]
+	GetHandleVerifier [0x0x7ff733fa6b55+79621]
+	GetHandleVerifier [0x0x7ff733fa6bb0+79712]
+	(No symbol) [0x0x7ff733d3c0ea]
+	(No symbol) [0x0x7ff733d92f56]
+	(No symbol) [0x0x7ff733d9320c]
+	(No symbol) [0x0x7ff733de65b7]
+	(No symbol) [0x0x7ff733dbb17f]
+	(No symbol) [0x0x7ff733de33d0]
+	(No symbol) [0x0x7ff733dbaf13]
+	(No symbol) [0x0x7ff733d84151]
+	(No symbol) [0x0x7ff733d84ee3]
+	GetHandleVerifier [0x0x7ff73426686d+2962461]
+	GetHandleVerifier [0x0x7ff734260b8d+2938685]
+	GetHandleVerifier [0x0x7ff73427f74d+3064573]
+	GetHandleVerifier [0x0x7ff733fc0c9e+186446]
+	GetHandleVerifier [0x0x7ff733fc8a6f+218655]
+	GetHandleVerifier [0x0x7ff733faf944+115956]
+	GetHandleVerifier [0x0x7ff733fafaf9+116393]
+	GetHandleVerifier [0x0x7ff733f95f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f66b55+79621]
-	GetHandleVerifier [0x0x7ff754f66bb0+79712]
-	(No symbol) [0x0x7ff754cfc0ea]
-	(No symbol) [0x0x7ff754d52f56]
-	(No symbol) [0x0x7ff754d5320c]
-	(No symbol) [0x0x7ff754da65b7]
-	(No symbol) [0x0x7ff754d7b17f]
-	(No symbol) [0x0x7ff754da33d0]
-	(No symbol) [0x0x7ff754d7af13]
-	(No symbol) [0x0x7ff754d44151]
-	(No symbol) [0x0x7ff754d44ee3]
-	GetHandleVerifier [0x0x7ff75522686d+2962461]
-	GetHandleVerifier [0x0x7ff755220b8d+2938685]
-	GetHandleVerifier [0x0x7ff75523f74d+3064573]
-	GetHandleVerifier [0x0x7ff754f80c9e+186446]
-	GetHandleVerifier [0x0x7ff754f88a6f+218655]
-	GetHandleVerifier [0x0x7ff754f6f944+115956]
-	GetHandleVerifier [0x0x7ff754f6faf9+116393]
-	GetHandleVerifier [0x0x7ff754f55f28+10968]
+	GetHandleVerifier [0x0x7ff733fa6b55+79621]
+	GetHandleVerifier [0x0x7ff733fa6bb0+79712]
+	(No symbol) [0x0x7ff733d3c0ea]
+	(No symbol) [0x0x7ff733d92f56]
+	(No symbol) [0x0x7ff733d9320c]
+	(No symbol) [0x0x7ff733de65b7]
+	(No symbol) [0x0x7ff733dbb17f]
+	(No symbol) [0x0x7ff733de33d0]
+	(No symbol) [0x0x7ff733dbaf13]
+	(No symbol) [0x0x7ff733d84151]
+	(No symbol) [0x0x7ff733d84ee3]
+	GetHandleVerifier [0x0x7ff73426686d+2962461]
+	GetHandleVerifier [0x0x7ff734260b8d+2938685]
+	GetHandleVerifier [0x0x7ff73427f74d+3064573]
+	GetHandleVerifier [0x0x7ff733fc0c9e+186446]
+	GetHandleVerifier [0x0x7ff733fc8a6f+218655]
+	GetHandleVerifier [0x0x7ff733faf944+115956]
+	GetHandleVerifier [0x0x7ff733fafaf9+116393]
+	GetHandleVerifier [0x0x7ff733f95f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f66b55+79621]
-	GetHandleVerifier [0x0x7ff754f66bb0+79712]
-	(No symbol) [0x0x7ff754cfc0ea]
-	(No symbol) [0x0x7ff754d52f56]
-	(No symbol) [0x0x7ff754d5320c]
-	(No symbol) [0x0x7ff754da65b7]
-	(No symbol) [0x0x7ff754d7b17f]
-	(No symbol) [0x0x7ff754da33d0]
-	(No symbol) [0x0x7ff754d7af13]
-	(No symbol) [0x0x7ff754d44151]
-	(No symbol) [0x0x7ff754d44ee3]
-	GetHandleVerifier [0x0x7ff75522686d+2962461]
-	GetHandleVerifier [0x0x7ff755220b8d+2938685]
-	GetHandleVerifier [0x0x7ff75523f74d+3064573]
-	GetHandleVerifier [0x0x7ff754f80c9e+186446]
-	GetHandleVerifier [0x0x7ff754f88a6f+218655]
-	GetHandleVerifier [0x0x7ff754f6f944+115956]
-	GetHandleVerifier [0x0x7ff754f6faf9+116393]
-	GetHandleVerifier [0x0x7ff754f55f28+10968]
+	GetHandleVerifier [0x0x7ff733fa6b55+79621]
+	GetHandleVerifier [0x0x7ff733fa6bb0+79712]
+	(No symbol) [0x0x7ff733d3c0ea]
+	(No symbol) [0x0x7ff733d92f56]
+	(No symbol) [0x0x7ff733d9320c]
+	(No symbol) [0x0x7ff733de65b7]
+	(No symbol) [0x0x7ff733dbb17f]
+	(No symbol) [0x0x7ff733de33d0]
+	(No symbol) [0x0x7ff733dbaf13]
+	(No symbol) [0x0x7ff733d84151]
+	(No symbol) [0x0x7ff733d84ee3]
+	GetHandleVerifier [0x0x7ff73426686d+2962461]
+	GetHandleVerifier [0x0x7ff734260b8d+2938685]
+	GetHandleVerifier [0x0x7ff73427f74d+3064573]
+	GetHandleVerifier [0x0x7ff733fc0c9e+186446]
+	GetHandleVerifier [0x0x7ff733fc8a6f+218655]
+	GetHandleVerifier [0x0x7ff733faf944+115956]
+	GetHandleVerifier [0x0x7ff733fafaf9+116393]
+	GetHandleVerifier [0x0x7ff733f95f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1642,19 +1642,19 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>£28.33</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>£28.60</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>£28.50</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>£28.60</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>£28.50</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>£31.00</t>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>£28.58</t>
+          <t>£27.29</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f66b55+79621]
-	GetHandleVerifier [0x0x7ff754f66bb0+79712]
-	(No symbol) [0x0x7ff754cfc0ea]
-	(No symbol) [0x0x7ff754d52f56]
-	(No symbol) [0x0x7ff754d5320c]
-	(No symbol) [0x0x7ff754da65b7]
-	(No symbol) [0x0x7ff754d7b17f]
-	(No symbol) [0x0x7ff754da33d0]
-	(No symbol) [0x0x7ff754d7af13]
-	(No symbol) [0x0x7ff754d44151]
-	(No symbol) [0x0x7ff754d44ee3]
-	GetHandleVerifier [0x0x7ff75522686d+2962461]
-	GetHandleVerifier [0x0x7ff755220b8d+2938685]
-	GetHandleVerifier [0x0x7ff75523f74d+3064573]
-	GetHandleVerifier [0x0x7ff754f80c9e+186446]
-	GetHandleVerifier [0x0x7ff754f88a6f+218655]
-	GetHandleVerifier [0x0x7ff754f6f944+115956]
-	GetHandleVerifier [0x0x7ff754f6faf9+116393]
-	GetHandleVerifier [0x0x7ff754f55f28+10968]
+	GetHandleVerifier [0x0x7ff733fa6b55+79621]
+	GetHandleVerifier [0x0x7ff733fa6bb0+79712]
+	(No symbol) [0x0x7ff733d3c0ea]
+	(No symbol) [0x0x7ff733d92f56]
+	(No symbol) [0x0x7ff733d9320c]
+	(No symbol) [0x0x7ff733de65b7]
+	(No symbol) [0x0x7ff733dbb17f]
+	(No symbol) [0x0x7ff733de33d0]
+	(No symbol) [0x0x7ff733dbaf13]
+	(No symbol) [0x0x7ff733d84151]
+	(No symbol) [0x0x7ff733d84ee3]
+	GetHandleVerifier [0x0x7ff73426686d+2962461]
+	GetHandleVerifier [0x0x7ff734260b8d+2938685]
+	GetHandleVerifier [0x0x7ff73427f74d+3064573]
+	GetHandleVerifier [0x0x7ff733fc0c9e+186446]
+	GetHandleVerifier [0x0x7ff733fc8a6f+218655]
+	GetHandleVerifier [0x0x7ff733faf944+115956]
+	GetHandleVerifier [0x0x7ff733fafaf9+116393]
+	GetHandleVerifier [0x0x7ff733f95f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f66b55+79621]
-	GetHandleVerifier [0x0x7ff754f66bb0+79712]
-	(No symbol) [0x0x7ff754cfc0ea]
-	(No symbol) [0x0x7ff754d52f56]
-	(No symbol) [0x0x7ff754d5320c]
-	(No symbol) [0x0x7ff754da65b7]
-	(No symbol) [0x0x7ff754d7b17f]
-	(No symbol) [0x0x7ff754da33d0]
-	(No symbol) [0x0x7ff754d7af13]
-	(No symbol) [0x0x7ff754d44151]
-	(No symbol) [0x0x7ff754d44ee3]
-	GetHandleVerifier [0x0x7ff75522686d+2962461]
-	GetHandleVerifier [0x0x7ff755220b8d+2938685]
-	GetHandleVerifier [0x0x7ff75523f74d+3064573]
-	GetHandleVerifier [0x0x7ff754f80c9e+186446]
-	GetHandleVerifier [0x0x7ff754f88a6f+218655]
-	GetHandleVerifier [0x0x7ff754f6f944+115956]
-	GetHandleVerifier [0x0x7ff754f6faf9+116393]
-	GetHandleVerifier [0x0x7ff754f55f28+10968]
+	GetHandleVerifier [0x0x7ff733fa6b55+79621]
+	GetHandleVerifier [0x0x7ff733fa6bb0+79712]
+	(No symbol) [0x0x7ff733d3c0ea]
+	(No symbol) [0x0x7ff733d92f56]
+	(No symbol) [0x0x7ff733d9320c]
+	(No symbol) [0x0x7ff733de65b7]
+	(No symbol) [0x0x7ff733dbb17f]
+	(No symbol) [0x0x7ff733de33d0]
+	(No symbol) [0x0x7ff733dbaf13]
+	(No symbol) [0x0x7ff733d84151]
+	(No symbol) [0x0x7ff733d84ee3]
+	GetHandleVerifier [0x0x7ff73426686d+2962461]
+	GetHandleVerifier [0x0x7ff734260b8d+2938685]
+	GetHandleVerifier [0x0x7ff73427f74d+3064573]
+	GetHandleVerifier [0x0x7ff733fc0c9e+186446]
+	GetHandleVerifier [0x0x7ff733fc8a6f+218655]
+	GetHandleVerifier [0x0x7ff733faf944+115956]
+	GetHandleVerifier [0x0x7ff733fafaf9+116393]
+	GetHandleVerifier [0x0x7ff733f95f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f66b55+79621]
-	GetHandleVerifier [0x0x7ff754f66bb0+79712]
-	(No symbol) [0x0x7ff754cfc0ea]
-	(No symbol) [0x0x7ff754d52f56]
-	(No symbol) [0x0x7ff754d5320c]
-	(No symbol) [0x0x7ff754da65b7]
-	(No symbol) [0x0x7ff754d7b17f]
-	(No symbol) [0x0x7ff754da33d0]
-	(No symbol) [0x0x7ff754d7af13]
-	(No symbol) [0x0x7ff754d44151]
-	(No symbol) [0x0x7ff754d44ee3]
-	GetHandleVerifier [0x0x7ff75522686d+2962461]
-	GetHandleVerifier [0x0x7ff755220b8d+2938685]
-	GetHandleVerifier [0x0x7ff75523f74d+3064573]
-	GetHandleVerifier [0x0x7ff754f80c9e+186446]
-	GetHandleVerifier [0x0x7ff754f88a6f+218655]
-	GetHandleVerifier [0x0x7ff754f6f944+115956]
-	GetHandleVerifier [0x0x7ff754f6faf9+116393]
-	GetHandleVerifier [0x0x7ff754f55f28+10968]
+	GetHandleVerifier [0x0x7ff733fa6b55+79621]
+	GetHandleVerifier [0x0x7ff733fa6bb0+79712]
+	(No symbol) [0x0x7ff733d3c0ea]
+	(No symbol) [0x0x7ff733d92f56]
+	(No symbol) [0x0x7ff733d9320c]
+	(No symbol) [0x0x7ff733de65b7]
+	(No symbol) [0x0x7ff733dbb17f]
+	(No symbol) [0x0x7ff733de33d0]
+	(No symbol) [0x0x7ff733dbaf13]
+	(No symbol) [0x0x7ff733d84151]
+	(No symbol) [0x0x7ff733d84ee3]
+	GetHandleVerifier [0x0x7ff73426686d+2962461]
+	GetHandleVerifier [0x0x7ff734260b8d+2938685]
+	GetHandleVerifier [0x0x7ff73427f74d+3064573]
+	GetHandleVerifier [0x0x7ff733fc0c9e+186446]
+	GetHandleVerifier [0x0x7ff733fc8a6f+218655]
+	GetHandleVerifier [0x0x7ff733faf944+115956]
+	GetHandleVerifier [0x0x7ff733fafaf9+116393]
+	GetHandleVerifier [0x0x7ff733f95f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f66b55+79621]
-	GetHandleVerifier [0x0x7ff754f66bb0+79712]
-	(No symbol) [0x0x7ff754cfc0ea]
-	(No symbol) [0x0x7ff754d52f56]
-	(No symbol) [0x0x7ff754d5320c]
-	(No symbol) [0x0x7ff754da65b7]
-	(No symbol) [0x0x7ff754d7b17f]
-	(No symbol) [0x0x7ff754da33d0]
-	(No symbol) [0x0x7ff754d7af13]
-	(No symbol) [0x0x7ff754d44151]
-	(No symbol) [0x0x7ff754d44ee3]
-	GetHandleVerifier [0x0x7ff75522686d+2962461]
-	GetHandleVerifier [0x0x7ff755220b8d+2938685]
-	GetHandleVerifier [0x0x7ff75523f74d+3064573]
-	GetHandleVerifier [0x0x7ff754f80c9e+186446]
-	GetHandleVerifier [0x0x7ff754f88a6f+218655]
-	GetHandleVerifier [0x0x7ff754f6f944+115956]
-	GetHandleVerifier [0x0x7ff754f6faf9+116393]
-	GetHandleVerifier [0x0x7ff754f55f28+10968]
+	GetHandleVerifier [0x0x7ff733fa6b55+79621]
+	GetHandleVerifier [0x0x7ff733fa6bb0+79712]
+	(No symbol) [0x0x7ff733d3c0ea]
+	(No symbol) [0x0x7ff733d92f56]
+	(No symbol) [0x0x7ff733d9320c]
+	(No symbol) [0x0x7ff733de65b7]
+	(No symbol) [0x0x7ff733dbb17f]
+	(No symbol) [0x0x7ff733de33d0]
+	(No symbol) [0x0x7ff733dbaf13]
+	(No symbol) [0x0x7ff733d84151]
+	(No symbol) [0x0x7ff733d84ee3]
+	GetHandleVerifier [0x0x7ff73426686d+2962461]
+	GetHandleVerifier [0x0x7ff734260b8d+2938685]
+	GetHandleVerifier [0x0x7ff73427f74d+3064573]
+	GetHandleVerifier [0x0x7ff733fc0c9e+186446]
+	GetHandleVerifier [0x0x7ff733fc8a6f+218655]
+	GetHandleVerifier [0x0x7ff733faf944+115956]
+	GetHandleVerifier [0x0x7ff733fafaf9+116393]
+	GetHandleVerifier [0x0x7ff733f95f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f66b55+79621]
-	GetHandleVerifier [0x0x7ff754f66bb0+79712]
-	(No symbol) [0x0x7ff754cfc0ea]
-	(No symbol) [0x0x7ff754d52f56]
-	(No symbol) [0x0x7ff754d5320c]
-	(No symbol) [0x0x7ff754da65b7]
-	(No symbol) [0x0x7ff754d7b17f]
-	(No symbol) [0x0x7ff754da33d0]
-	(No symbol) [0x0x7ff754d7af13]
-	(No symbol) [0x0x7ff754d44151]
-	(No symbol) [0x0x7ff754d44ee3]
-	GetHandleVerifier [0x0x7ff75522686d+2962461]
-	GetHandleVerifier [0x0x7ff755220b8d+2938685]
-	GetHandleVerifier [0x0x7ff75523f74d+3064573]
-	GetHandleVerifier [0x0x7ff754f80c9e+186446]
-	GetHandleVerifier [0x0x7ff754f88a6f+218655]
-	GetHandleVerifier [0x0x7ff754f6f944+115956]
-	GetHandleVerifier [0x0x7ff754f6faf9+116393]
-	GetHandleVerifier [0x0x7ff754f55f28+10968]
+	GetHandleVerifier [0x0x7ff733fa6b55+79621]
+	GetHandleVerifier [0x0x7ff733fa6bb0+79712]
+	(No symbol) [0x0x7ff733d3c0ea]
+	(No symbol) [0x0x7ff733d92f56]
+	(No symbol) [0x0x7ff733d9320c]
+	(No symbol) [0x0x7ff733de65b7]
+	(No symbol) [0x0x7ff733dbb17f]
+	(No symbol) [0x0x7ff733de33d0]
+	(No symbol) [0x0x7ff733dbaf13]
+	(No symbol) [0x0x7ff733d84151]
+	(No symbol) [0x0x7ff733d84ee3]
+	GetHandleVerifier [0x0x7ff73426686d+2962461]
+	GetHandleVerifier [0x0x7ff734260b8d+2938685]
+	GetHandleVerifier [0x0x7ff73427f74d+3064573]
+	GetHandleVerifier [0x0x7ff733fc0c9e+186446]
+	GetHandleVerifier [0x0x7ff733fc8a6f+218655]
+	GetHandleVerifier [0x0x7ff733faf944+115956]
+	GetHandleVerifier [0x0x7ff733fafaf9+116393]
+	GetHandleVerifier [0x0x7ff733f95f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f66b55+79621]
-	GetHandleVerifier [0x0x7ff754f66bb0+79712]
-	(No symbol) [0x0x7ff754cfc0ea]
-	(No symbol) [0x0x7ff754d52f56]
-	(No symbol) [0x0x7ff754d5320c]
-	(No symbol) [0x0x7ff754da65b7]
-	(No symbol) [0x0x7ff754d7b17f]
-	(No symbol) [0x0x7ff754da33d0]
-	(No symbol) [0x0x7ff754d7af13]
-	(No symbol) [0x0x7ff754d44151]
-	(No symbol) [0x0x7ff754d44ee3]
-	GetHandleVerifier [0x0x7ff75522686d+2962461]
-	GetHandleVerifier [0x0x7ff755220b8d+2938685]
-	GetHandleVerifier [0x0x7ff75523f74d+3064573]
-	GetHandleVerifier [0x0x7ff754f80c9e+186446]
-	GetHandleVerifier [0x0x7ff754f88a6f+218655]
-	GetHandleVerifier [0x0x7ff754f6f944+115956]
-	GetHandleVerifier [0x0x7ff754f6faf9+116393]
-	GetHandleVerifier [0x0x7ff754f55f28+10968]
+	GetHandleVerifier [0x0x7ff733fa6b55+79621]
+	GetHandleVerifier [0x0x7ff733fa6bb0+79712]
+	(No symbol) [0x0x7ff733d3c0ea]
+	(No symbol) [0x0x7ff733d92f56]
+	(No symbol) [0x0x7ff733d9320c]
+	(No symbol) [0x0x7ff733de65b7]
+	(No symbol) [0x0x7ff733dbb17f]
+	(No symbol) [0x0x7ff733de33d0]
+	(No symbol) [0x0x7ff733dbaf13]
+	(No symbol) [0x0x7ff733d84151]
+	(No symbol) [0x0x7ff733d84ee3]
+	GetHandleVerifier [0x0x7ff73426686d+2962461]
+	GetHandleVerifier [0x0x7ff734260b8d+2938685]
+	GetHandleVerifier [0x0x7ff73427f74d+3064573]
+	GetHandleVerifier [0x0x7ff733fc0c9e+186446]
+	GetHandleVerifier [0x0x7ff733fc8a6f+218655]
+	GetHandleVerifier [0x0x7ff733faf944+115956]
+	GetHandleVerifier [0x0x7ff733fafaf9+116393]
+	GetHandleVerifier [0x0x7ff733f95f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f66b55+79621]
-	GetHandleVerifier [0x0x7ff754f66bb0+79712]
-	(No symbol) [0x0x7ff754cfc0ea]
-	(No symbol) [0x0x7ff754d52f56]
-	(No symbol) [0x0x7ff754d5320c]
-	(No symbol) [0x0x7ff754da65b7]
-	(No symbol) [0x0x7ff754d7b17f]
-	(No symbol) [0x0x7ff754da33d0]
-	(No symbol) [0x0x7ff754d7af13]
-	(No symbol) [0x0x7ff754d44151]
-	(No symbol) [0x0x7ff754d44ee3]
-	GetHandleVerifier [0x0x7ff75522686d+2962461]
-	GetHandleVerifier [0x0x7ff755220b8d+2938685]
-	GetHandleVerifier [0x0x7ff75523f74d+3064573]
-	GetHandleVerifier [0x0x7ff754f80c9e+186446]
-	GetHandleVerifier [0x0x7ff754f88a6f+218655]
-	GetHandleVerifier [0x0x7ff754f6f944+115956]
-	GetHandleVerifier [0x0x7ff754f6faf9+116393]
-	GetHandleVerifier [0x0x7ff754f55f28+10968]
+	GetHandleVerifier [0x0x7ff733fa6b55+79621]
+	GetHandleVerifier [0x0x7ff733fa6bb0+79712]
+	(No symbol) [0x0x7ff733d3c0ea]
+	(No symbol) [0x0x7ff733d92f56]
+	(No symbol) [0x0x7ff733d9320c]
+	(No symbol) [0x0x7ff733de65b7]
+	(No symbol) [0x0x7ff733dbb17f]
+	(No symbol) [0x0x7ff733de33d0]
+	(No symbol) [0x0x7ff733dbaf13]
+	(No symbol) [0x0x7ff733d84151]
+	(No symbol) [0x0x7ff733d84ee3]
+	GetHandleVerifier [0x0x7ff73426686d+2962461]
+	GetHandleVerifier [0x0x7ff734260b8d+2938685]
+	GetHandleVerifier [0x0x7ff73427f74d+3064573]
+	GetHandleVerifier [0x0x7ff733fc0c9e+186446]
+	GetHandleVerifier [0x0x7ff733fc8a6f+218655]
+	GetHandleVerifier [0x0x7ff733faf944+115956]
+	GetHandleVerifier [0x0x7ff733fafaf9+116393]
+	GetHandleVerifier [0x0x7ff733f95f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f66b55+79621]
-	GetHandleVerifier [0x0x7ff754f66bb0+79712]
-	(No symbol) [0x0x7ff754cfc0ea]
-	(No symbol) [0x0x7ff754d52f56]
-	(No symbol) [0x0x7ff754d5320c]
-	(No symbol) [0x0x7ff754da65b7]
-	(No symbol) [0x0x7ff754d7b17f]
-	(No symbol) [0x0x7ff754da33d0]
-	(No symbol) [0x0x7ff754d7af13]
-	(No symbol) [0x0x7ff754d44151]
-	(No symbol) [0x0x7ff754d44ee3]
-	GetHandleVerifier [0x0x7ff75522686d+2962461]
-	GetHandleVerifier [0x0x7ff755220b8d+2938685]
-	GetHandleVerifier [0x0x7ff75523f74d+3064573]
-	GetHandleVerifier [0x0x7ff754f80c9e+186446]
-	GetHandleVerifier [0x0x7ff754f88a6f+218655]
-	GetHandleVerifier [0x0x7ff754f6f944+115956]
-	GetHandleVerifier [0x0x7ff754f6faf9+116393]
-	GetHandleVerifier [0x0x7ff754f55f28+10968]
+	GetHandleVerifier [0x0x7ff733fa6b55+79621]
+	GetHandleVerifier [0x0x7ff733fa6bb0+79712]
+	(No symbol) [0x0x7ff733d3c0ea]
+	(No symbol) [0x0x7ff733d92f56]
+	(No symbol) [0x0x7ff733d9320c]
+	(No symbol) [0x0x7ff733de65b7]
+	(No symbol) [0x0x7ff733dbb17f]
+	(No symbol) [0x0x7ff733de33d0]
+	(No symbol) [0x0x7ff733dbaf13]
+	(No symbol) [0x0x7ff733d84151]
+	(No symbol) [0x0x7ff733d84ee3]
+	GetHandleVerifier [0x0x7ff73426686d+2962461]
+	GetHandleVerifier [0x0x7ff734260b8d+2938685]
+	GetHandleVerifier [0x0x7ff73427f74d+3064573]
+	GetHandleVerifier [0x0x7ff733fc0c9e+186446]
+	GetHandleVerifier [0x0x7ff733fc8a6f+218655]
+	GetHandleVerifier [0x0x7ff733faf944+115956]
+	GetHandleVerifier [0x0x7ff733fafaf9+116393]
+	GetHandleVerifier [0x0x7ff733f95f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f66b55+79621]
-	GetHandleVerifier [0x0x7ff754f66bb0+79712]
-	(No symbol) [0x0x7ff754cfc0ea]
-	(No symbol) [0x0x7ff754d52f56]
-	(No symbol) [0x0x7ff754d5320c]
-	(No symbol) [0x0x7ff754da65b7]
-	(No symbol) [0x0x7ff754d7b17f]
-	(No symbol) [0x0x7ff754da33d0]
-	(No symbol) [0x0x7ff754d7af13]
-	(No symbol) [0x0x7ff754d44151]
-	(No symbol) [0x0x7ff754d44ee3]
-	GetHandleVerifier [0x0x7ff75522686d+2962461]
-	GetHandleVerifier [0x0x7ff755220b8d+2938685]
-	GetHandleVerifier [0x0x7ff75523f74d+3064573]
-	GetHandleVerifier [0x0x7ff754f80c9e+186446]
-	GetHandleVerifier [0x0x7ff754f88a6f+218655]
-	GetHandleVerifier [0x0x7ff754f6f944+115956]
-	GetHandleVerifier [0x0x7ff754f6faf9+116393]
-	GetHandleVerifier [0x0x7ff754f55f28+10968]
+	GetHandleVerifier [0x0x7ff733fa6b55+79621]
+	GetHandleVerifier [0x0x7ff733fa6bb0+79712]
+	(No symbol) [0x0x7ff733d3c0ea]
+	(No symbol) [0x0x7ff733d92f56]
+	(No symbol) [0x0x7ff733d9320c]
+	(No symbol) [0x0x7ff733de65b7]
+	(No symbol) [0x0x7ff733dbb17f]
+	(No symbol) [0x0x7ff733de33d0]
+	(No symbol) [0x0x7ff733dbaf13]
+	(No symbol) [0x0x7ff733d84151]
+	(No symbol) [0x0x7ff733d84ee3]
+	GetHandleVerifier [0x0x7ff73426686d+2962461]
+	GetHandleVerifier [0x0x7ff734260b8d+2938685]
+	GetHandleVerifier [0x0x7ff73427f74d+3064573]
+	GetHandleVerifier [0x0x7ff733fc0c9e+186446]
+	GetHandleVerifier [0x0x7ff733fc8a6f+218655]
+	GetHandleVerifier [0x0x7ff733faf944+115956]
+	GetHandleVerifier [0x0x7ff733fafaf9+116393]
+	GetHandleVerifier [0x0x7ff733f95f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f66b55+79621]
-	GetHandleVerifier [0x0x7ff754f66bb0+79712]
-	(No symbol) [0x0x7ff754cfc0ea]
-	(No symbol) [0x0x7ff754d52f56]
-	(No symbol) [0x0x7ff754d5320c]
-	(No symbol) [0x0x7ff754da65b7]
-	(No symbol) [0x0x7ff754d7b17f]
-	(No symbol) [0x0x7ff754da33d0]
-	(No symbol) [0x0x7ff754d7af13]
-	(No symbol) [0x0x7ff754d44151]
-	(No symbol) [0x0x7ff754d44ee3]
-	GetHandleVerifier [0x0x7ff75522686d+2962461]
-	GetHandleVerifier [0x0x7ff755220b8d+2938685]
-	GetHandleVerifier [0x0x7ff75523f74d+3064573]
-	GetHandleVerifier [0x0x7ff754f80c9e+186446]
-	GetHandleVerifier [0x0x7ff754f88a6f+218655]
-	GetHandleVerifier [0x0x7ff754f6f944+115956]
-	GetHandleVerifier [0x0x7ff754f6faf9+116393]
-	GetHandleVerifier [0x0x7ff754f55f28+10968]
+	GetHandleVerifier [0x0x7ff733fa6b55+79621]
+	GetHandleVerifier [0x0x7ff733fa6bb0+79712]
+	(No symbol) [0x0x7ff733d3c0ea]
+	(No symbol) [0x0x7ff733d92f56]
+	(No symbol) [0x0x7ff733d9320c]
+	(No symbol) [0x0x7ff733de65b7]
+	(No symbol) [0x0x7ff733dbb17f]
+	(No symbol) [0x0x7ff733de33d0]
+	(No symbol) [0x0x7ff733dbaf13]
+	(No symbol) [0x0x7ff733d84151]
+	(No symbol) [0x0x7ff733d84ee3]
+	GetHandleVerifier [0x0x7ff73426686d+2962461]
+	GetHandleVerifier [0x0x7ff734260b8d+2938685]
+	GetHandleVerifier [0x0x7ff73427f74d+3064573]
+	GetHandleVerifier [0x0x7ff733fc0c9e+186446]
+	GetHandleVerifier [0x0x7ff733fc8a6f+218655]
+	GetHandleVerifier [0x0x7ff733faf944+115956]
+	GetHandleVerifier [0x0x7ff733fafaf9+116393]
+	GetHandleVerifier [0x0x7ff733f95f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f66b55+79621]
-	GetHandleVerifier [0x0x7ff754f66bb0+79712]
-	(No symbol) [0x0x7ff754cfc0ea]
-	(No symbol) [0x0x7ff754d52f56]
-	(No symbol) [0x0x7ff754d5320c]
-	(No symbol) [0x0x7ff754da65b7]
-	(No symbol) [0x0x7ff754d7b17f]
-	(No symbol) [0x0x7ff754da33d0]
-	(No symbol) [0x0x7ff754d7af13]
-	(No symbol) [0x0x7ff754d44151]
-	(No symbol) [0x0x7ff754d44ee3]
-	GetHandleVerifier [0x0x7ff75522686d+2962461]
-	GetHandleVerifier [0x0x7ff755220b8d+2938685]
-	GetHandleVerifier [0x0x7ff75523f74d+3064573]
-	GetHandleVerifier [0x0x7ff754f80c9e+186446]
-	GetHandleVerifier [0x0x7ff754f88a6f+218655]
-	GetHandleVerifier [0x0x7ff754f6f944+115956]
-	GetHandleVerifier [0x0x7ff754f6faf9+116393]
-	GetHandleVerifier [0x0x7ff754f55f28+10968]
+	GetHandleVerifier [0x0x7ff733fa6b55+79621]
+	GetHandleVerifier [0x0x7ff733fa6bb0+79712]
+	(No symbol) [0x0x7ff733d3c0ea]
+	(No symbol) [0x0x7ff733d92f56]
+	(No symbol) [0x0x7ff733d9320c]
+	(No symbol) [0x0x7ff733de65b7]
+	(No symbol) [0x0x7ff733dbb17f]
+	(No symbol) [0x0x7ff733de33d0]
+	(No symbol) [0x0x7ff733dbaf13]
+	(No symbol) [0x0x7ff733d84151]
+	(No symbol) [0x0x7ff733d84ee3]
+	GetHandleVerifier [0x0x7ff73426686d+2962461]
+	GetHandleVerifier [0x0x7ff734260b8d+2938685]
+	GetHandleVerifier [0x0x7ff73427f74d+3064573]
+	GetHandleVerifier [0x0x7ff733fc0c9e+186446]
+	GetHandleVerifier [0x0x7ff733fc8a6f+218655]
+	GetHandleVerifier [0x0x7ff733faf944+115956]
+	GetHandleVerifier [0x0x7ff733fafaf9+116393]
+	GetHandleVerifier [0x0x7ff733f95f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -3108,25 +3108,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f66b55+79621]
-	GetHandleVerifier [0x0x7ff754f66bb0+79712]
-	(No symbol) [0x0x7ff754cfc0ea]
-	(No symbol) [0x0x7ff754d52f56]
-	(No symbol) [0x0x7ff754d5320c]
-	(No symbol) [0x0x7ff754da65b7]
-	(No symbol) [0x0x7ff754d7b17f]
-	(No symbol) [0x0x7ff754da33d0]
-	(No symbol) [0x0x7ff754d7af13]
-	(No symbol) [0x0x7ff754d44151]
-	(No symbol) [0x0x7ff754d44ee3]
-	GetHandleVerifier [0x0x7ff75522686d+2962461]
-	GetHandleVerifier [0x0x7ff755220b8d+2938685]
-	GetHandleVerifier [0x0x7ff75523f74d+3064573]
-	GetHandleVerifier [0x0x7ff754f80c9e+186446]
-	GetHandleVerifier [0x0x7ff754f88a6f+218655]
-	GetHandleVerifier [0x0x7ff754f6f944+115956]
-	GetHandleVerifier [0x0x7ff754f6faf9+116393]
-	GetHandleVerifier [0x0x7ff754f55f28+10968]
+	GetHandleVerifier [0x0x7ff733fa6b55+79621]
+	GetHandleVerifier [0x0x7ff733fa6bb0+79712]
+	(No symbol) [0x0x7ff733d3c0ea]
+	(No symbol) [0x0x7ff733d92f56]
+	(No symbol) [0x0x7ff733d9320c]
+	(No symbol) [0x0x7ff733de65b7]
+	(No symbol) [0x0x7ff733dbb17f]
+	(No symbol) [0x0x7ff733de33d0]
+	(No symbol) [0x0x7ff733dbaf13]
+	(No symbol) [0x0x7ff733d84151]
+	(No symbol) [0x0x7ff733d84ee3]
+	GetHandleVerifier [0x0x7ff73426686d+2962461]
+	GetHandleVerifier [0x0x7ff734260b8d+2938685]
+	GetHandleVerifier [0x0x7ff73427f74d+3064573]
+	GetHandleVerifier [0x0x7ff733fc0c9e+186446]
+	GetHandleVerifier [0x0x7ff733fc8a6f+218655]
+	GetHandleVerifier [0x0x7ff733faf944+115956]
+	GetHandleVerifier [0x0x7ff733fafaf9+116393]
+	GetHandleVerifier [0x0x7ff733f95f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -3229,25 +3229,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f66b55+79621]
-	GetHandleVerifier [0x0x7ff754f66bb0+79712]
-	(No symbol) [0x0x7ff754cfc0ea]
-	(No symbol) [0x0x7ff754d52f56]
-	(No symbol) [0x0x7ff754d5320c]
-	(No symbol) [0x0x7ff754da65b7]
-	(No symbol) [0x0x7ff754d7b17f]
-	(No symbol) [0x0x7ff754da33d0]
-	(No symbol) [0x0x7ff754d7af13]
-	(No symbol) [0x0x7ff754d44151]
-	(No symbol) [0x0x7ff754d44ee3]
-	GetHandleVerifier [0x0x7ff75522686d+2962461]
-	GetHandleVerifier [0x0x7ff755220b8d+2938685]
-	GetHandleVerifier [0x0x7ff75523f74d+3064573]
-	GetHandleVerifier [0x0x7ff754f80c9e+186446]
-	GetHandleVerifier [0x0x7ff754f88a6f+218655]
-	GetHandleVerifier [0x0x7ff754f6f944+115956]
-	GetHandleVerifier [0x0x7ff754f6faf9+116393]
-	GetHandleVerifier [0x0x7ff754f55f28+10968]
+	GetHandleVerifier [0x0x7ff733fa6b55+79621]
+	GetHandleVerifier [0x0x7ff733fa6bb0+79712]
+	(No symbol) [0x0x7ff733d3c0ea]
+	(No symbol) [0x0x7ff733d92f56]
+	(No symbol) [0x0x7ff733d9320c]
+	(No symbol) [0x0x7ff733de65b7]
+	(No symbol) [0x0x7ff733dbb17f]
+	(No symbol) [0x0x7ff733de33d0]
+	(No symbol) [0x0x7ff733dbaf13]
+	(No symbol) [0x0x7ff733d84151]
+	(No symbol) [0x0x7ff733d84ee3]
+	GetHandleVerifier [0x0x7ff73426686d+2962461]
+	GetHandleVerifier [0x0x7ff734260b8d+2938685]
+	GetHandleVerifier [0x0x7ff73427f74d+3064573]
+	GetHandleVerifier [0x0x7ff733fc0c9e+186446]
+	GetHandleVerifier [0x0x7ff733fc8a6f+218655]
+	GetHandleVerifier [0x0x7ff733faf944+115956]
+	GetHandleVerifier [0x0x7ff733fafaf9+116393]
+	GetHandleVerifier [0x0x7ff733f95f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -3350,25 +3350,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f66b55+79621]
-	GetHandleVerifier [0x0x7ff754f66bb0+79712]
-	(No symbol) [0x0x7ff754cfc0ea]
-	(No symbol) [0x0x7ff754d52f56]
-	(No symbol) [0x0x7ff754d5320c]
-	(No symbol) [0x0x7ff754da65b7]
-	(No symbol) [0x0x7ff754d7b17f]
-	(No symbol) [0x0x7ff754da33d0]
-	(No symbol) [0x0x7ff754d7af13]
-	(No symbol) [0x0x7ff754d44151]
-	(No symbol) [0x0x7ff754d44ee3]
-	GetHandleVerifier [0x0x7ff75522686d+2962461]
-	GetHandleVerifier [0x0x7ff755220b8d+2938685]
-	GetHandleVerifier [0x0x7ff75523f74d+3064573]
-	GetHandleVerifier [0x0x7ff754f80c9e+186446]
-	GetHandleVerifier [0x0x7ff754f88a6f+218655]
-	GetHandleVerifier [0x0x7ff754f6f944+115956]
-	GetHandleVerifier [0x0x7ff754f6faf9+116393]
-	GetHandleVerifier [0x0x7ff754f55f28+10968]
+	GetHandleVerifier [0x0x7ff733fa6b55+79621]
+	GetHandleVerifier [0x0x7ff733fa6bb0+79712]
+	(No symbol) [0x0x7ff733d3c0ea]
+	(No symbol) [0x0x7ff733d92f56]
+	(No symbol) [0x0x7ff733d9320c]
+	(No symbol) [0x0x7ff733de65b7]
+	(No symbol) [0x0x7ff733dbb17f]
+	(No symbol) [0x0x7ff733de33d0]
+	(No symbol) [0x0x7ff733dbaf13]
+	(No symbol) [0x0x7ff733d84151]
+	(No symbol) [0x0x7ff733d84ee3]
+	GetHandleVerifier [0x0x7ff73426686d+2962461]
+	GetHandleVerifier [0x0x7ff734260b8d+2938685]
+	GetHandleVerifier [0x0x7ff73427f74d+3064573]
+	GetHandleVerifier [0x0x7ff733fc0c9e+186446]
+	GetHandleVerifier [0x0x7ff733fc8a6f+218655]
+	GetHandleVerifier [0x0x7ff733faf944+115956]
+	GetHandleVerifier [0x0x7ff733fafaf9+116393]
+	GetHandleVerifier [0x0x7ff733f95f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
@@ -3471,25 +3471,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=139.0.7258.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff754f66b55+79621]
-	GetHandleVerifier [0x0x7ff754f66bb0+79712]
-	(No symbol) [0x0x7ff754cfc0ea]
-	(No symbol) [0x0x7ff754d52f56]
-	(No symbol) [0x0x7ff754d5320c]
-	(No symbol) [0x0x7ff754da65b7]
-	(No symbol) [0x0x7ff754d7b17f]
-	(No symbol) [0x0x7ff754da33d0]
-	(No symbol) [0x0x7ff754d7af13]
-	(No symbol) [0x0x7ff754d44151]
-	(No symbol) [0x0x7ff754d44ee3]
-	GetHandleVerifier [0x0x7ff75522686d+2962461]
-	GetHandleVerifier [0x0x7ff755220b8d+2938685]
-	GetHandleVerifier [0x0x7ff75523f74d+3064573]
-	GetHandleVerifier [0x0x7ff754f80c9e+186446]
-	GetHandleVerifier [0x0x7ff754f88a6f+218655]
-	GetHandleVerifier [0x0x7ff754f6f944+115956]
-	GetHandleVerifier [0x0x7ff754f6faf9+116393]
-	GetHandleVerifier [0x0x7ff754f55f28+10968]
+	GetHandleVerifier [0x0x7ff733fa6b55+79621]
+	GetHandleVerifier [0x0x7ff733fa6bb0+79712]
+	(No symbol) [0x0x7ff733d3c0ea]
+	(No symbol) [0x0x7ff733d92f56]
+	(No symbol) [0x0x7ff733d9320c]
+	(No symbol) [0x0x7ff733de65b7]
+	(No symbol) [0x0x7ff733dbb17f]
+	(No symbol) [0x0x7ff733de33d0]
+	(No symbol) [0x0x7ff733dbaf13]
+	(No symbol) [0x0x7ff733d84151]
+	(No symbol) [0x0x7ff733d84ee3]
+	GetHandleVerifier [0x0x7ff73426686d+2962461]
+	GetHandleVerifier [0x0x7ff734260b8d+2938685]
+	GetHandleVerifier [0x0x7ff73427f74d+3064573]
+	GetHandleVerifier [0x0x7ff733fc0c9e+186446]
+	GetHandleVerifier [0x0x7ff733fc8a6f+218655]
+	GetHandleVerifier [0x0x7ff733faf944+115956]
+	GetHandleVerifier [0x0x7ff733fafaf9+116393]
+	GetHandleVerifier [0x0x7ff733f95f28+10968]
 	BaseThreadInitThunk [0x0x7ffde661e8d7+23]
 	RtlUserThreadStart [0x0x7ffde699c34c+44]
 </t>
